--- a/Regionalied FeliX/Model Files/TotalPopulationbyAge.xlsx
+++ b/Regionalied FeliX/Model Files/TotalPopulationbyAge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iiasahub-my.sharepoint.com/personal/yequanliang_iiasa_ac_at/Documents/research_iiasa/Felix-Model/version_oct_2023/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iiasahub-my.sharepoint.com/personal/yequanliang_iiasa_ac_at/Documents/research_iiasa/Felix-Model/Regionalied FeliX/Model Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3770" documentId="13_ncr:1_{FE6EE77C-DE09-4F18-A09F-03FA1D28A0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C546F660-7C89-4520-B6A5-A56D86690FA7}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" tabRatio="759" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" tabRatio="759" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -2217,10 +2217,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="32.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -2917,7 +2917,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6D42E3-31AE-4069-9DF9-41DA8DBFAF44}">
   <dimension ref="A1:AZ60"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:52">
       <c r="A1" s="1" t="s">
@@ -4930,9 +4930,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5324F484-0FE1-49A6-BC7F-7B3474F04FB2}">
   <dimension ref="A1:GT11"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="47.875" customWidth="1"/>
+    <col min="1" max="1" width="47.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:202">
@@ -11631,10 +11631,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E59E882-B849-40B5-8A7C-732F77C9EF42}">
   <dimension ref="A1:EV121"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:152">
@@ -12750,7 +12750,7 @@
         <v>0.30149024800000002</v>
       </c>
       <c r="DN3">
-        <f t="shared" ref="DN3:EV3" si="2">-0.006039*(DN$1-2023)+$BW3</f>
+        <f t="shared" ref="DN3:ET3" si="2">-0.006039*(DN$1-2023)+$BW3</f>
         <v>0.29545124800000006</v>
       </c>
       <c r="DO3">
@@ -14539,7 +14539,7 @@
         <v>0.13662633800000001</v>
       </c>
       <c r="BY12">
-        <f t="shared" ref="BY12:CN13" si="3">-0.005743*(BY$1-2023)+$BW12</f>
+        <f t="shared" ref="BY12:CJ13" si="3">-0.005743*(BY$1-2023)+$BW12</f>
         <v>0.13088333800000002</v>
       </c>
       <c r="BZ12">
@@ -14782,7 +14782,7 @@
         <v>0.412332119</v>
       </c>
       <c r="CE13">
-        <f t="shared" ref="CE12:CW13" si="4">-0.005743*(CE$1-2023)+$BW13</f>
+        <f t="shared" ref="CE13:CW13" si="4">-0.005743*(CE$1-2023)+$BW13</f>
         <v>0.406589119</v>
       </c>
       <c r="CF13">
@@ -14858,7 +14858,7 @@
         <v>0.30321511899999998</v>
       </c>
       <c r="CX13">
-        <f t="shared" ref="CX13:EV13" si="5">-0.005743*(CX$1-2023)+$BW13</f>
+        <f t="shared" ref="CX13:EF13" si="5">-0.005743*(CX$1-2023)+$BW13</f>
         <v>0.29747211899999998</v>
       </c>
       <c r="CY13">
@@ -16756,7 +16756,7 @@
         <v>0.41835401800000005</v>
       </c>
       <c r="DI21">
-        <f t="shared" ref="DI20:DX21" si="8">0.003743*(DI$1-2023)+$BW21</f>
+        <f t="shared" ref="DI21:DX21" si="8">0.003743*(DI$1-2023)+$BW21</f>
         <v>0.42209701799999999</v>
       </c>
       <c r="DJ21">
@@ -16820,7 +16820,7 @@
         <v>0.47824201799999999</v>
       </c>
       <c r="DY21">
-        <f t="shared" ref="DY21:EW21" si="9">0.003743*(DY$1-2023)+$BW21</f>
+        <f t="shared" ref="DY21:EV21" si="9">0.003743*(DY$1-2023)+$BW21</f>
         <v>0.48198501800000004</v>
       </c>
       <c r="DZ21">
@@ -17663,7 +17663,7 @@
         <v>0.31661256700000001</v>
       </c>
       <c r="EK23">
-        <f t="shared" ref="EK22:EV23" si="11">-0.006039*(EK$1-2023)+$BW23</f>
+        <f t="shared" ref="EK23:EV23" si="11">-0.006039*(EK$1-2023)+$BW23</f>
         <v>0.31057356700000005</v>
       </c>
       <c r="EL23">
@@ -19700,7 +19700,7 @@
         <v>0.29701446399999998</v>
       </c>
       <c r="BY33">
-        <f t="shared" ref="BY32:EJ33" si="12">-0.005743*(BY$1-2023)+$BW33</f>
+        <f t="shared" ref="BY33:DF33" si="12">-0.005743*(BY$1-2023)+$BW33</f>
         <v>0.29127146399999998</v>
       </c>
       <c r="BZ33">
@@ -21851,7 +21851,7 @@
         <v>0.56721482300000003</v>
       </c>
       <c r="EK41">
-        <f t="shared" ref="EK40:EV41" si="14">0.003743*(EK$1-2023)+$BW41</f>
+        <f t="shared" ref="EK41:EV41" si="14">0.003743*(EK$1-2023)+$BW41</f>
         <v>0.57095782299999998</v>
       </c>
       <c r="EL41">
@@ -22195,7 +22195,7 @@
         <v>0.58802379699999996</v>
       </c>
       <c r="BY43">
-        <f t="shared" ref="BY42:EJ43" si="15">-0.006039*(BY$1-2023)+$BW43</f>
+        <f t="shared" ref="BY43:EJ43" si="15">-0.006039*(BY$1-2023)+$BW43</f>
         <v>0.58198479699999994</v>
       </c>
       <c r="BZ43">
@@ -22451,7 +22451,7 @@
         <v>0.20152779699999995</v>
       </c>
       <c r="EK43">
-        <f t="shared" ref="EK42:EV43" si="16">-0.006039*(EK$1-2023)+$BW43</f>
+        <f t="shared" ref="EK43:EV43" si="16">-0.006039*(EK$1-2023)+$BW43</f>
         <v>0.19548879699999999</v>
       </c>
       <c r="EL43">
@@ -23933,7 +23933,7 @@
         <v>0.44654257800000002</v>
       </c>
       <c r="BY53">
-        <f t="shared" ref="BY52:EJ53" si="17">-0.005743*(BY$1-2023)+$BW53</f>
+        <f t="shared" ref="BY53:EF53" si="17">-0.005743*(BY$1-2023)+$BW53</f>
         <v>0.44079957800000003</v>
       </c>
       <c r="BZ53">
@@ -25315,7 +25315,7 @@
         <v>0.37026426000000001</v>
       </c>
       <c r="BY61">
-        <f t="shared" ref="BY60:EJ61" si="18">0.003743*(BY$1-2023)+$BW61</f>
+        <f t="shared" ref="BY61:EJ61" si="18">0.003743*(BY$1-2023)+$BW61</f>
         <v>0.37400726000000001</v>
       </c>
       <c r="BZ61">
@@ -25571,7 +25571,7 @@
         <v>0.60981626</v>
       </c>
       <c r="EK61">
-        <f t="shared" ref="EK60:EV61" si="19">0.003743*(EK$1-2023)+$BW61</f>
+        <f t="shared" ref="EK61:EL61" si="19">0.003743*(EK$1-2023)+$BW61</f>
         <v>0.61355925999999994</v>
       </c>
       <c r="EL61">
@@ -26389,7 +26389,7 @@
         <v>0.37536387199999993</v>
       </c>
       <c r="EK63">
-        <f t="shared" ref="EK62:EV63" si="21">-0.006039*(EK$1-2023)+$BW63</f>
+        <f t="shared" ref="EK63:EV63" si="21">-0.006039*(EK$1-2023)+$BW63</f>
         <v>0.36932487199999997</v>
       </c>
       <c r="EL63">
@@ -28671,7 +28671,7 @@
         <v>0.19729558500000005</v>
       </c>
       <c r="EK73">
-        <f t="shared" ref="EK72:EV73" si="23">-0.005743*(EK$1-2023)+$BW73</f>
+        <f t="shared" ref="EK73:EV73" si="23">-0.005743*(EK$1-2023)+$BW73</f>
         <v>0.19155258500000005</v>
       </c>
       <c r="EL73">
@@ -30570,7 +30570,7 @@
         <v>0.60214016699999995</v>
       </c>
       <c r="EK81">
-        <f t="shared" ref="EK80:EV81" si="25">0.003743*(EK$1-2023)+$BW81</f>
+        <f t="shared" ref="EK81:EN81" si="25">0.003743*(EK$1-2023)+$BW81</f>
         <v>0.605883167</v>
       </c>
       <c r="EL81">
@@ -31456,7 +31456,7 @@
         <v>0.32108167599999998</v>
       </c>
       <c r="EK83">
-        <f t="shared" ref="EK82:EV83" si="27">-0.006039*(EK$1-2023)+$BW83</f>
+        <f t="shared" ref="EK83:EV83" si="27">-0.006039*(EK$1-2023)+$BW83</f>
         <v>0.31504267600000002</v>
       </c>
       <c r="EL83">
@@ -33960,7 +33960,7 @@
         <v>0.30142575700000002</v>
       </c>
       <c r="EK93">
-        <f t="shared" ref="EK92:EV93" si="29">-0.005743*(EK$1-2023)+$BW93</f>
+        <f t="shared" ref="EK93:EV93" si="29">-0.005743*(EK$1-2023)+$BW93</f>
         <v>0.29568275700000002</v>
       </c>
       <c r="EL93">
@@ -35594,7 +35594,7 @@
         <v>0.52074836400000002</v>
       </c>
       <c r="BY101">
-        <f t="shared" ref="BY100:EJ101" si="30">0.003743*(BY$1-2023)+$BW101</f>
+        <f t="shared" ref="BY101:CX101" si="30">0.003743*(BY$1-2023)+$BW101</f>
         <v>0.52449136399999996</v>
       </c>
       <c r="BZ101">
@@ -36328,7 +36328,7 @@
         <v>0.31919511399999995</v>
       </c>
       <c r="EK103">
-        <f t="shared" ref="EK102:EV103" si="32">-0.006039*(EK$1-2023)+$BW103</f>
+        <f t="shared" ref="EK103:EV103" si="32">-0.006039*(EK$1-2023)+$BW103</f>
         <v>0.31315611399999999</v>
       </c>
       <c r="EL103">
@@ -37532,7 +37532,7 @@
         <v>0.16255122</v>
       </c>
       <c r="BY112">
-        <f t="shared" ref="BY112:EJ113" si="33">-0.005743*(BY$1-2023)+$BW112</f>
+        <f t="shared" ref="BY112:EB113" si="33">-0.005743*(BY$1-2023)+$BW112</f>
         <v>0.15680822</v>
       </c>
       <c r="BZ112">
@@ -38825,7 +38825,7 @@
         <v>0.56146258100000002</v>
       </c>
       <c r="BY120">
-        <f t="shared" ref="BY120:EJ121" si="34">0.003743*(BY$1-2023)+$BW120</f>
+        <f t="shared" ref="BY120:EE121" si="34">0.003743*(BY$1-2023)+$BW120</f>
         <v>0.56520558099999996</v>
       </c>
       <c r="BZ120">
@@ -39264,9 +39264,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FD85EF-37EB-4123-A4C3-C965158C9156}">
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -39391,11 +39391,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3949D677-618C-4222-8B38-AA313138C934}">
   <dimension ref="A1:GX215"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="108" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="108" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:206">
@@ -46086,7 +46086,7 @@
         <v>84368700000000</v>
       </c>
     </row>
-    <row r="14" spans="1:206" s="3" customFormat="1" ht="114.15">
+    <row r="14" spans="1:206" s="3" customFormat="1" ht="115.2">
       <c r="A14" s="3" t="s">
         <v>227</v>
       </c>
@@ -51952,10 +51952,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590B2F13-8BF4-46F8-AB0D-088E1CB7A18E}">
   <dimension ref="A1:BB26"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="39.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="36" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="36" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54">
@@ -54485,10 +54485,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F435F0-16FC-4215-A558-F31299898FF6}">
   <dimension ref="A1:BA108"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="39.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="36" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="36" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53">
@@ -58582,7 +58582,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176011A1-7261-4BED-8449-EF434E939937}">
   <dimension ref="A1:BJ82"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="1" t="s">
@@ -61346,7 +61346,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8661702D-5D5A-4D04-B969-700ADB1555D9}">
   <dimension ref="A1:AZ60"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:52">
       <c r="A1" s="1" t="s">
